--- a/XLibur.Tests/Resource/Examples/Misc/SheetProtection.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/SheetProtection.xlsx
@@ -445,7 +445,7 @@
   <x:dimension ref="A1:B4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26.424911" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26.853482" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Misc/SheetProtection.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/SheetProtection.xlsx
@@ -445,7 +445,7 @@
   <x:dimension ref="A1:B4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="27.567768" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
